--- a/public/MotorsASF.xlsx
+++ b/public/MotorsASF.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ru0nntr\Desktop\Прочее\Linear Motion Calculator\project_v0.96\public\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ru0nntr\Desktop\Прочее\Linear Motion Calculator\project_v0.97\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -161,12 +161,6 @@
     <t>mot_pic</t>
   </si>
   <si>
-    <t>https://smarta.ru/upload/iblock/7e6/s7ux3cbdzbpaw5w5ec0jax8tlb8ypfgv/EMMR_AS_BC_P_small_1.png</t>
-  </si>
-  <si>
-    <t>https://smarta.ru/upload/iblock/626/setjqkjevv8wqwc18qtalpo8e1dqg077/EMMR_AS_BC_big_1.png</t>
-  </si>
-  <si>
     <t>calc_reductionRatio</t>
   </si>
   <si>
@@ -195,6 +189,12 @@
   </si>
   <si>
     <t>mot_GBtype</t>
+  </si>
+  <si>
+    <t>./pics/emmr-as-b_c-40_60_80.png</t>
+  </si>
+  <si>
+    <t>./pics/emmr-as-b_c-130_180.png</t>
   </si>
 </sst>
 </file>
@@ -557,19 +557,19 @@
         <v>44</v>
       </c>
       <c r="L1" t="s">
+        <v>46</v>
+      </c>
+      <c r="M1" t="s">
+        <v>45</v>
+      </c>
+      <c r="N1" t="s">
+        <v>47</v>
+      </c>
+      <c r="O1" t="s">
         <v>48</v>
       </c>
-      <c r="M1" t="s">
-        <v>47</v>
-      </c>
-      <c r="N1" t="s">
-        <v>49</v>
-      </c>
-      <c r="O1" t="s">
-        <v>50</v>
-      </c>
       <c r="P1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
@@ -604,7 +604,7 @@
         <v>3000</v>
       </c>
       <c r="K2" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="N2">
         <v>40</v>
@@ -613,7 +613,7 @@
         <v>0</v>
       </c>
       <c r="P2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.3">
@@ -648,7 +648,7 @@
         <v>3000</v>
       </c>
       <c r="K3" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="N3">
         <v>40</v>
@@ -657,7 +657,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.3">
@@ -692,7 +692,7 @@
         <v>3000</v>
       </c>
       <c r="K4" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="N4">
         <v>60</v>
@@ -701,7 +701,7 @@
         <v>0</v>
       </c>
       <c r="P4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.3">
@@ -736,7 +736,7 @@
         <v>3000</v>
       </c>
       <c r="K5" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="N5">
         <v>60</v>
@@ -745,7 +745,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.3">
@@ -780,7 +780,7 @@
         <v>3000</v>
       </c>
       <c r="K6" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="N6">
         <v>60</v>
@@ -789,7 +789,7 @@
         <v>0</v>
       </c>
       <c r="P6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.3">
@@ -824,7 +824,7 @@
         <v>3000</v>
       </c>
       <c r="K7" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="N7">
         <v>60</v>
@@ -833,7 +833,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.3">
@@ -868,7 +868,7 @@
         <v>3000</v>
       </c>
       <c r="K8" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="N8">
         <v>80</v>
@@ -877,7 +877,7 @@
         <v>0</v>
       </c>
       <c r="P8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.3">
@@ -912,7 +912,7 @@
         <v>3000</v>
       </c>
       <c r="K9" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="N9">
         <v>80</v>
@@ -921,7 +921,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.3">
@@ -956,7 +956,7 @@
         <v>3000</v>
       </c>
       <c r="K10" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="N10">
         <v>80</v>
@@ -965,7 +965,7 @@
         <v>0</v>
       </c>
       <c r="P10" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.3">
@@ -1000,7 +1000,7 @@
         <v>3000</v>
       </c>
       <c r="K11" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="N11">
         <v>80</v>
@@ -1009,7 +1009,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.3">
@@ -1044,7 +1044,7 @@
         <v>1500</v>
       </c>
       <c r="K12" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="N12">
         <v>130</v>
@@ -1053,7 +1053,7 @@
         <v>0</v>
       </c>
       <c r="P12" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.3">
@@ -1088,7 +1088,7 @@
         <v>1500</v>
       </c>
       <c r="K13" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="N13">
         <v>130</v>
@@ -1097,7 +1097,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.3">
@@ -1132,7 +1132,7 @@
         <v>1500</v>
       </c>
       <c r="K14" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="N14">
         <v>130</v>
@@ -1141,7 +1141,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.3">
@@ -1176,7 +1176,7 @@
         <v>1500</v>
       </c>
       <c r="K15" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="N15">
         <v>130</v>
@@ -1185,7 +1185,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.3">
@@ -1220,7 +1220,7 @@
         <v>1500</v>
       </c>
       <c r="K16" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="N16">
         <v>130</v>
@@ -1229,7 +1229,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.3">
@@ -1264,7 +1264,7 @@
         <v>1500</v>
       </c>
       <c r="K17" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="N17">
         <v>130</v>
@@ -1273,7 +1273,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.3">
@@ -1308,7 +1308,7 @@
         <v>2500</v>
       </c>
       <c r="K18" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="N18">
         <v>130</v>
@@ -1317,7 +1317,7 @@
         <v>0</v>
       </c>
       <c r="P18" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.3">
@@ -1352,7 +1352,7 @@
         <v>2500</v>
       </c>
       <c r="K19" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="N19">
         <v>130</v>
@@ -1361,7 +1361,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.3">
@@ -1396,7 +1396,7 @@
         <v>2500</v>
       </c>
       <c r="K20" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="N20">
         <v>130</v>
@@ -1405,7 +1405,7 @@
         <v>0</v>
       </c>
       <c r="P20" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.3">
@@ -1440,7 +1440,7 @@
         <v>2500</v>
       </c>
       <c r="K21" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="N21">
         <v>130</v>
@@ -1449,7 +1449,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.3">
@@ -1484,7 +1484,7 @@
         <v>2500</v>
       </c>
       <c r="K22" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="N22">
         <v>130</v>
@@ -1493,7 +1493,7 @@
         <v>0</v>
       </c>
       <c r="P22" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.3">
@@ -1528,7 +1528,7 @@
         <v>2500</v>
       </c>
       <c r="K23" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="N23">
         <v>130</v>
@@ -1537,7 +1537,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.3">
@@ -1572,7 +1572,7 @@
         <v>2500</v>
       </c>
       <c r="K24" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="N24">
         <v>130</v>
@@ -1581,7 +1581,7 @@
         <v>0</v>
       </c>
       <c r="P24" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.3">
@@ -1616,7 +1616,7 @@
         <v>2500</v>
       </c>
       <c r="K25" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="N25">
         <v>130</v>
@@ -1625,7 +1625,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.3">
@@ -1660,7 +1660,7 @@
         <v>2500</v>
       </c>
       <c r="K26" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="N26">
         <v>130</v>
@@ -1669,7 +1669,7 @@
         <v>0</v>
       </c>
       <c r="P26" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.3">
@@ -1704,7 +1704,7 @@
         <v>2500</v>
       </c>
       <c r="K27" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="N27">
         <v>130</v>
@@ -1713,7 +1713,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.3">
@@ -1748,7 +1748,7 @@
         <v>1500</v>
       </c>
       <c r="K28" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="N28">
         <v>180</v>
@@ -1757,7 +1757,7 @@
         <v>0</v>
       </c>
       <c r="P28" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.3">
@@ -1792,7 +1792,7 @@
         <v>1500</v>
       </c>
       <c r="K29" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="N29">
         <v>180</v>
@@ -1801,7 +1801,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.3">
@@ -1836,7 +1836,7 @@
         <v>2000</v>
       </c>
       <c r="K30" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="N30">
         <v>180</v>
@@ -1845,7 +1845,7 @@
         <v>0</v>
       </c>
       <c r="P30" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.3">
@@ -1880,7 +1880,7 @@
         <v>2000</v>
       </c>
       <c r="K31" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="N31">
         <v>180</v>
@@ -1889,7 +1889,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.3">
@@ -1924,7 +1924,7 @@
         <v>1500</v>
       </c>
       <c r="K32" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="N32">
         <v>180</v>
@@ -1933,7 +1933,7 @@
         <v>0</v>
       </c>
       <c r="P32" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.3">
@@ -1968,7 +1968,7 @@
         <v>1500</v>
       </c>
       <c r="K33" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="N33">
         <v>180</v>
@@ -1977,7 +1977,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.3">
@@ -2012,7 +2012,7 @@
         <v>1500</v>
       </c>
       <c r="K34" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="N34">
         <v>180</v>
@@ -2021,7 +2021,7 @@
         <v>0</v>
       </c>
       <c r="P34" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.3">
@@ -2056,7 +2056,7 @@
         <v>1500</v>
       </c>
       <c r="K35" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="N35">
         <v>180</v>
@@ -2065,7 +2065,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
